--- a/results_diabetes_korea_simple.xlsx
+++ b/results_diabetes_korea_simple.xlsx
@@ -551,7 +551,7 @@
         <v>1.67</v>
       </c>
       <c r="H2">
-        <v>7855</v>
+        <v>5058</v>
       </c>
       <c r="I2">
         <v>-1.660731206821651</v>
@@ -578,58 +578,58 @@
         <v>13.82599798902785</v>
       </c>
       <c r="Q2">
-        <v>0.6769554448593391</v>
+        <v>0.5870720902752697</v>
       </c>
       <c r="R2">
-        <v>0.3254537890667784</v>
+        <v>0.1644894705132682</v>
       </c>
       <c r="S2">
-        <v>0.8256437760794945</v>
+        <v>0.7975996679104673</v>
       </c>
       <c r="T2">
-        <v>5317.48501937011</v>
+        <v>2969.410632612315</v>
       </c>
       <c r="U2">
-        <v>2556.439513119544</v>
+        <v>831.9877418561103</v>
       </c>
       <c r="V2">
-        <v>6485.431861104429</v>
+        <v>4034.259120291144</v>
       </c>
       <c r="W2">
-        <v>383.7592721363108</v>
+        <v>332.8052972561477</v>
       </c>
       <c r="X2">
-        <v>184.496498484066</v>
+        <v>93.24743593926658</v>
       </c>
       <c r="Y2">
-        <v>468.0492002217046</v>
+        <v>452.1512757417648</v>
       </c>
       <c r="Z2">
-        <v>4623.789535271488</v>
+        <v>3590.616994077282</v>
       </c>
       <c r="AA2">
-        <v>2163.189482566324</v>
+        <v>1014.69533773315</v>
       </c>
       <c r="AB2">
-        <v>6912.804310593957</v>
+        <v>5924.601890641003</v>
       </c>
       <c r="AC2">
-        <v>5305.854924827427</v>
+        <v>4601.365370601316</v>
       </c>
       <c r="AD2">
-        <v>2550.848217023377</v>
+        <v>1289.238861778303</v>
       </c>
       <c r="AE2">
-        <v>6471.247301031383</v>
+        <v>6251.442629142019</v>
       </c>
       <c r="AF2">
-        <v>9959.374027093705</v>
+        <v>8256.359381866694</v>
       </c>
       <c r="AG2">
-        <v>4886.106346788335</v>
+        <v>2378.815668067314</v>
       </c>
       <c r="AH2">
-        <v>13063.45916041361</v>
+        <v>11923.69531234987</v>
       </c>
     </row>
     <row r="3">
@@ -657,7 +657,7 @@
         <v>2.11</v>
       </c>
       <c r="H3">
-        <v>10666</v>
+        <v>8084</v>
       </c>
       <c r="I3">
         <v>-1.514127732629776</v>
@@ -684,58 +684,58 @@
         <v>17.75734615707216</v>
       </c>
       <c r="Q3">
-        <v>0.751569512307089</v>
+        <v>0.646384793833898</v>
       </c>
       <c r="R3">
-        <v>0.4166166691376174</v>
+        <v>0.2270728566173505</v>
       </c>
       <c r="S3">
-        <v>0.8938962471122412</v>
+        <v>0.8546410213867927</v>
       </c>
       <c r="T3">
-        <v>8016.240418267412</v>
+        <v>5225.374673353232</v>
       </c>
       <c r="U3">
-        <v>4443.633393021827</v>
+        <v>1835.656972894662</v>
       </c>
       <c r="V3">
-        <v>9534.297371699164</v>
+        <v>6908.918016890832</v>
       </c>
       <c r="W3">
-        <v>537.6277349337531</v>
+        <v>462.3848984211406</v>
       </c>
       <c r="X3">
-        <v>298.0225681009033</v>
+        <v>162.4342972526555</v>
       </c>
       <c r="Y3">
-        <v>639.4397414092707</v>
+        <v>611.3589082388283</v>
       </c>
       <c r="Z3">
-        <v>6408.597720447829</v>
+        <v>5812.316521155291</v>
       </c>
       <c r="AA3">
-        <v>3222.593943830894</v>
+        <v>1910.514940576921</v>
       </c>
       <c r="AB3">
-        <v>9392.546495758741</v>
+        <v>9404.559598160215</v>
       </c>
       <c r="AC3">
-        <v>9546.841792861291</v>
+        <v>8210.728699066844</v>
       </c>
       <c r="AD3">
-        <v>5292.089904387351</v>
+        <v>2884.40204409616</v>
       </c>
       <c r="AE3">
-        <v>11354.75283479313</v>
+        <v>10856.11175980659</v>
       </c>
       <c r="AF3">
-        <v>16002.5520766779</v>
+        <v>14170.71176638363</v>
       </c>
       <c r="AG3">
-        <v>8760.869428147402</v>
+        <v>4946.254955142805</v>
       </c>
       <c r="AH3">
-        <v>20264.08520885761</v>
+        <v>19712.12571718003</v>
       </c>
     </row>
   </sheetData>

--- a/results_diabetes_korea_simple.xlsx
+++ b/results_diabetes_korea_simple.xlsx
@@ -569,13 +569,13 @@
         <v>0.19</v>
       </c>
       <c r="N2">
-        <v>18.2</v>
+        <v>19.10000000000001</v>
       </c>
       <c r="O2">
-        <v>566.89</v>
+        <v>599.79</v>
       </c>
       <c r="P2">
-        <v>13.82599798902785</v>
+        <v>13.16585805031761</v>
       </c>
       <c r="Q2">
         <v>0.5870720902752697</v>
@@ -596,40 +596,40 @@
         <v>4034.259120291144</v>
       </c>
       <c r="W2">
-        <v>332.8052972561477</v>
+        <v>352.119969026204</v>
       </c>
       <c r="X2">
-        <v>93.24743593926658</v>
+        <v>98.6591395191531</v>
       </c>
       <c r="Y2">
-        <v>452.1512757417648</v>
+        <v>478.3923048160191</v>
       </c>
       <c r="Z2">
-        <v>3590.616994077282</v>
+        <v>3768.174977300885</v>
       </c>
       <c r="AA2">
-        <v>1014.69533773315</v>
+        <v>1064.872579708965</v>
       </c>
       <c r="AB2">
-        <v>5924.601890641003</v>
+        <v>6217.576709408966</v>
       </c>
       <c r="AC2">
-        <v>4601.365370601316</v>
+        <v>4635.961528881237</v>
       </c>
       <c r="AD2">
-        <v>1289.238861778303</v>
+        <v>1298.93222627565</v>
       </c>
       <c r="AE2">
-        <v>6251.442629142019</v>
+        <v>6298.445177571983</v>
       </c>
       <c r="AF2">
-        <v>8256.359381866694</v>
+        <v>8464.562611046293</v>
       </c>
       <c r="AG2">
-        <v>2378.815668067314</v>
+        <v>2444.509306135591</v>
       </c>
       <c r="AH2">
-        <v>11923.69531234987</v>
+        <v>12254.99596989226</v>
       </c>
     </row>
     <row r="3">
@@ -675,13 +675,13 @@
         <v>0.22</v>
       </c>
       <c r="N3">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="O3">
-        <v>715.34</v>
+        <v>783.0599999999999</v>
       </c>
       <c r="P3">
-        <v>17.75734615707216</v>
+        <v>16.50964166219702</v>
       </c>
       <c r="Q3">
         <v>0.646384793833898</v>
@@ -702,40 +702,40 @@
         <v>6908.918016890832</v>
       </c>
       <c r="W3">
-        <v>462.3848984211406</v>
+        <v>506.1580766595721</v>
       </c>
       <c r="X3">
-        <v>162.4342972526555</v>
+        <v>177.8116711027825</v>
       </c>
       <c r="Y3">
-        <v>611.3589082388283</v>
+        <v>669.2351982071419</v>
       </c>
       <c r="Z3">
-        <v>5812.316521155291</v>
+        <v>6195.163717159534</v>
       </c>
       <c r="AA3">
-        <v>1910.514940576921</v>
+        <v>2036.357242052048</v>
       </c>
       <c r="AB3">
-        <v>9404.559598160215</v>
+        <v>10024.02160761988</v>
       </c>
       <c r="AC3">
-        <v>8210.728699066844</v>
+        <v>8356.488470076387</v>
       </c>
       <c r="AD3">
-        <v>2884.40204409616</v>
+        <v>2935.606973263372</v>
       </c>
       <c r="AE3">
-        <v>10856.11175980659</v>
+        <v>11048.83331012931</v>
       </c>
       <c r="AF3">
-        <v>14170.71176638363</v>
+        <v>14700.37930785513</v>
       </c>
       <c r="AG3">
-        <v>4946.254955142805</v>
+        <v>5116.256551601713</v>
       </c>
       <c r="AH3">
-        <v>19712.12571718003</v>
+        <v>20524.10064557077</v>
       </c>
     </row>
   </sheetData>
